--- a/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/practice_completed.xlsx
+++ b/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/practice_completed.xlsx
@@ -490,8 +490,8 @@
     <col width="13.5" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="16.5" customWidth="1" min="5" max="5"/>
-    <col width="15.5" customWidth="1" min="6" max="6"/>
+    <col width="19.5" customWidth="1" min="5" max="5"/>
+    <col width="14.5" customWidth="1" min="6" max="6"/>
     <col width="22.5" customWidth="1" min="7" max="7"/>
     <col width="12.5" customWidth="1" min="8" max="8"/>
     <col width="10.5" customWidth="1" min="9" max="9"/>
@@ -569,12 +569,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -657,12 +657,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -789,12 +789,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sofia Lopez</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4265,12 +4265,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
